--- a/YasamEndeksi.xlsx
+++ b/YasamEndeksi.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DDFE1C-1566-42A9-A40E-4D2A70A8CFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C99D7F-8AF9-4B3B-9F61-6B3B3E7DFEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A2FF6C02-068F-4AE2-A68D-76658AAEC360}"/>
   </bookViews>
@@ -103,9 +103,6 @@
     <t>Gümüşhane</t>
   </si>
   <si>
-    <t>Hakkari</t>
-  </si>
-  <si>
     <t>Hatay</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t xml:space="preserve">Genel Endeks </t>
+  </si>
+  <si>
+    <t>Hakkâri</t>
   </si>
 </sst>
 </file>
@@ -716,658 +716,658 @@
   <sheetData>
     <row r="1" spans="1:2" s="3" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="7">
-        <v>0.67449519306006811</v>
+        <v>4.4189999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="B3" s="7">
-        <v>0.67371640415330658</v>
+        <v>2.8370000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B4" s="7">
-        <v>0.65534971577433265</v>
+        <v>1.8080000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B5" s="7">
-        <v>0.65200418807765648</v>
+        <v>1.7769999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7">
-        <v>0.649418381168405</v>
+        <v>1.716</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="B7" s="7">
-        <v>0.64849429488125632</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B8" s="7">
-        <v>0.63155451547349839</v>
+        <v>1.2949999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B9" s="7">
-        <v>0.63145891869916437</v>
+        <v>1.2509999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B10" s="7">
-        <v>0.63127200910689496</v>
+        <v>0.98299999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B11" s="7">
-        <v>0.62751488347604145</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B12" s="7">
-        <v>0.62698076190319696</v>
+        <v>0.81899999999999995</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B13" s="7">
-        <v>0.62622350524831338</v>
+        <v>0.72899999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B14" s="7">
-        <v>0.62564817532698735</v>
+        <v>0.68799999999999994</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B15" s="7">
-        <v>0.62516414549708388</v>
+        <v>0.68100000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>0.62183994906585049</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="B17" s="7">
-        <v>0.62127814546574434</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B18" s="7">
-        <v>0.61903655552631554</v>
+        <v>0.61499999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B19" s="7">
-        <v>0.61634698190534609</v>
+        <v>0.59699999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7">
-        <v>0.60406383433065181</v>
+        <v>0.55600000000000005</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B21" s="7">
-        <v>0.60070502950764704</v>
+        <v>0.50900000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B22" s="7">
-        <v>0.59957886608684519</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="B23" s="7">
-        <v>0.59815993005035828</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B24" s="7">
-        <v>0.59305696939414443</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="B25" s="7">
-        <v>0.59228717624805494</v>
+        <v>0.42099999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="B26" s="7">
-        <v>0.58964397387655265</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="27" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B27" s="7">
-        <v>0.58927143360776957</v>
+        <v>0.31900000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B28" s="7">
-        <v>0.58875838521668411</v>
+        <v>0.31900000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B29" s="7">
-        <v>0.58627195957369493</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="B30" s="7">
-        <v>0.58479290460205402</v>
+        <v>0.16500000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B31" s="7">
-        <v>0.58062017630813978</v>
+        <v>0.14699999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B32" s="7">
-        <v>0.58015084823164953</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="33" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B33" s="7">
-        <v>0.57801970624927312</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="34" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B34" s="7">
-        <v>0.57461955410496823</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="35" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B35" s="7">
-        <v>0.57229041036938244</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="36" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B36" s="7">
-        <v>0.56790374496894547</v>
+        <v>7.9000000000000001E-2</v>
       </c>
     </row>
     <row r="37" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B37" s="7">
-        <v>0.56730420752301236</v>
+        <v>6.2E-2</v>
       </c>
     </row>
     <row r="38" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B38" s="7">
-        <v>0.56402662523660396</v>
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="39" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B39" s="7">
-        <v>0.56359729672139747</v>
+        <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="40" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="B40" s="7">
-        <v>0.56193245198532404</v>
+        <v>-6.9000000000000006E-2</v>
       </c>
     </row>
     <row r="41" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B41" s="7">
-        <v>0.55915076978275657</v>
+        <v>-0.129</v>
       </c>
     </row>
     <row r="42" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="B42" s="7">
-        <v>0.55328901490227211</v>
+        <v>-0.13500000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B43" s="7">
-        <v>0.55044312024454645</v>
+        <v>-0.14799999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B44" s="7">
-        <v>0.54638479476311241</v>
+        <v>-0.157</v>
       </c>
     </row>
     <row r="45" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B45" s="7">
-        <v>0.54579631101517689</v>
+        <v>-0.159</v>
       </c>
     </row>
     <row r="46" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B46" s="7">
-        <v>0.54457196219831805</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="47" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B47" s="7">
-        <v>0.54297268762640838</v>
+        <v>-0.16600000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="B48" s="7">
-        <v>0.53906086335888259</v>
+        <v>-0.17399999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="B49" s="7">
-        <v>0.53280438750432102</v>
+        <v>-0.184</v>
       </c>
     </row>
     <row r="50" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="B50" s="7">
-        <v>0.53063032723550074</v>
+        <v>-0.191</v>
       </c>
     </row>
     <row r="51" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51" s="7">
-        <v>0.53058638647814904</v>
+        <v>-0.247</v>
       </c>
     </row>
     <row r="52" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B52" s="7">
-        <v>0.52980586978242772</v>
+        <v>-0.25900000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B53" s="7">
-        <v>0.52841564729735535</v>
+        <v>-0.28000000000000003</v>
       </c>
     </row>
     <row r="54" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B54" s="7">
-        <v>0.51883912155322465</v>
+        <v>-0.28299999999999997</v>
       </c>
     </row>
     <row r="55" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B55" s="7">
-        <v>0.51346178717731172</v>
+        <v>-0.312</v>
       </c>
     </row>
     <row r="56" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>0.50859932267516217</v>
+        <v>-0.34699999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="B57" s="7">
-        <v>0.50019436847681975</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="58" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B58" s="7">
-        <v>0.49101054120787668</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="59" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B59" s="7">
-        <v>0.48297445148150825</v>
+        <v>-0.38100000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B60" s="7">
-        <v>0.4771984835240724</v>
+        <v>-0.38400000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B61" s="7">
-        <v>0.47163415774000833</v>
+        <v>-0.46600000000000003</v>
       </c>
     </row>
     <row r="62" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B62" s="7">
-        <v>0.46782130752089662</v>
+        <v>-0.47599999999999998</v>
       </c>
     </row>
     <row r="63" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B63" s="7">
-        <v>0.4463696487370129</v>
+        <v>-0.52400000000000002</v>
       </c>
     </row>
     <row r="64" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B64" s="7">
-        <v>0.44158120333590245</v>
+        <v>-0.57999999999999996</v>
       </c>
     </row>
     <row r="65" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="B65" s="7">
-        <v>0.44018946096113609</v>
+        <v>-0.60099999999999998</v>
       </c>
     </row>
     <row r="66" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B66" s="7">
-        <v>0.42402469912653262</v>
+        <v>-0.873</v>
       </c>
     </row>
     <row r="67" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="B67" s="7">
-        <v>0.41270346637864902</v>
+        <v>-0.88100000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B68" s="7">
-        <v>0.39537445121993192</v>
+        <v>-0.92900000000000005</v>
       </c>
     </row>
     <row r="69" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="B69" s="7">
-        <v>0.39520427247206097</v>
+        <v>-0.93700000000000006</v>
       </c>
     </row>
     <row r="70" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B70" s="7">
-        <v>0.3796337950261886</v>
+        <v>-0.94399999999999995</v>
       </c>
     </row>
     <row r="71" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B71" s="7">
-        <v>0.37924212055897616</v>
+        <v>-0.98499999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B72" s="7">
-        <v>0.36619329014206853</v>
+        <v>-1.1160000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B73" s="7">
-        <v>0.3621135660071389</v>
+        <v>-1.1739999999999999</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B74" s="7">
-        <v>0.35403565259602549</v>
+        <v>-1.1819999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B75" s="7">
-        <v>0.35269058434285372</v>
+        <v>-1.345</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B76" s="7">
-        <v>0.34887736567439748</v>
+        <v>-1.3480000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B77" s="7">
-        <v>0.33254020384258615</v>
+        <v>-1.353</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B78" s="7">
-        <v>0.32216448441097828</v>
+        <v>-1.4710000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B79" s="7">
-        <v>0.32054434878318305</v>
+        <v>-1.4970000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="B80" s="7">
-        <v>0.29747171657303878</v>
+        <v>-1.5249999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B81" s="7">
-        <v>0.29363581417278223</v>
+        <v>-1.7969999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="B82" s="9">
-        <v>0.2765215315637487</v>
+        <v>-1.8260000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.2">
